--- a/src/static/Acc3.xlsx
+++ b/src/static/Acc3.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ЭтаКнига" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lysenyj.nikolay\Desktop\калькулятор\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lysenyj.nikolay\calc\acc_conf\src\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A76FBF87-93E8-47DD-8A59-4A41D1BF4ACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9122662B-CC71-40C7-ABD0-F79D406B6419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F2BABEBC-3656-4A0D-978D-B963CC88D9B4}"/>
   </bookViews>
@@ -8927,23 +8927,23 @@
         <v>250</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A160" t="s">
+    <row r="160" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A160" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B160" t="s">
+      <c r="B160" s="22" t="s">
         <v>133</v>
       </c>
-      <c r="F160" s="9">
-        <v>3</v>
-      </c>
-      <c r="G160" t="s">
+      <c r="F160" s="23">
+        <v>3</v>
+      </c>
+      <c r="G160" s="22" t="s">
         <v>292</v>
       </c>
-      <c r="H160" t="s">
+      <c r="H160" s="22" t="s">
         <v>302</v>
       </c>
-      <c r="J160" t="s">
+      <c r="J160" s="22" t="s">
         <v>252</v>
       </c>
     </row>
@@ -9430,26 +9430,26 @@
         <v>250</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A181" t="s">
+    <row r="181" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A181" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B181" t="s">
+      <c r="B181" s="22" t="s">
         <v>133</v>
       </c>
-      <c r="F181" s="9">
-        <v>3</v>
-      </c>
-      <c r="G181" t="s">
+      <c r="F181" s="23">
+        <v>3</v>
+      </c>
+      <c r="G181" s="22" t="s">
         <v>292</v>
       </c>
-      <c r="H181" t="s">
+      <c r="H181" s="22" t="s">
         <v>302</v>
       </c>
-      <c r="I181" t="s">
+      <c r="I181" s="22" t="s">
         <v>367</v>
       </c>
-      <c r="J181" t="s">
+      <c r="J181" s="22" t="s">
         <v>252</v>
       </c>
     </row>
